--- a/results/assignmentModel.xlsx
+++ b/results/assignmentModel.xlsx
@@ -1,29 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10511"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/begumyilmaz/Documents/okul/koç/4.2/bitirme/bitirmeRepoYeni/indr491/results/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F30A930-FB15-834F-B9F8-F20635D1FCE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="740" windowWidth="30240" windowHeight="18900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$154</definedName>
-  </definedNames>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="466" uniqueCount="182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="478" uniqueCount="184">
   <si>
     <t>SpecGroupId</t>
   </si>
@@ -55,7 +46,7 @@
     <t>(1200.0x0.8xS280GD+Z)</t>
   </si>
   <si>
-    <t>(1220.0x1.0xDX51D+Z)</t>
+    <t>(1200.0x1.2xDX51D+Z)</t>
   </si>
   <si>
     <t>(1200.0x1.2xS280GD+Z)</t>
@@ -97,19 +88,25 @@
     <t>(1000.0x1.0xDX51D+Z)</t>
   </si>
   <si>
-    <t>(1040.0x1.0xDX51D+Z)</t>
-  </si>
-  <si>
     <t>(1250.0x3.0xDX51D+Z)</t>
   </si>
   <si>
     <t>(986.0x1.8xDX51D+Z)</t>
   </si>
   <si>
-    <t>(1140.0x0.5xDX51D+Z)</t>
-  </si>
-  <si>
-    <t>(1150.0x0.8xDX51D+Z)</t>
+    <t>(1130.0x0.5xDX51DT+Z)</t>
+  </si>
+  <si>
+    <t>(1150.0x0.5xDX51D+Z)</t>
+  </si>
+  <si>
+    <t>(1170.0x0.5xDX51DT+Z)</t>
+  </si>
+  <si>
+    <t>(1136.0x0.8xDX51D+Z)</t>
+  </si>
+  <si>
+    <t>(1140.0x1.0xDX51D+Z)</t>
   </si>
   <si>
     <t>(1500.0x2.0xS275J2)</t>
@@ -118,6 +115,9 @@
     <t>(980.0x4.0xS350GD+Z)</t>
   </si>
   <si>
+    <t>(1170.0x4.0xS350GD+Z)</t>
+  </si>
+  <si>
     <t>(950.0x1.2xS350GD+Z)</t>
   </si>
   <si>
@@ -133,7 +133,7 @@
     <t>(1274.0x2.6xS350GD+Z)</t>
   </si>
   <si>
-    <t>(1220.0x0.5xDX51DT+Z)</t>
+    <t>(1220.0x0.6xDX51DT+Z)</t>
   </si>
   <si>
     <t>(1000.0x5.0xDD11)</t>
@@ -196,12 +196,12 @@
     <t>(1250.0x1.5xDX51D+Z)</t>
   </si>
   <si>
+    <t>(1500.0x1.5xS350GD+Z)</t>
+  </si>
+  <si>
     <t>(1500.0x2.0xDX51D+Z)</t>
   </si>
   <si>
-    <t>(1500.0x3.0xDD11)</t>
-  </si>
-  <si>
     <t>(1500.0x3.0xDX51D+Z)</t>
   </si>
   <si>
@@ -220,6 +220,9 @@
     <t>(1000.0x0.5xDX51D+Z)</t>
   </si>
   <si>
+    <t>(1000.0x0.66xDX51D+Z)</t>
+  </si>
+  <si>
     <t>(1000.0x0.7xDX51D+Z)</t>
   </si>
   <si>
@@ -235,9 +238,6 @@
     <t>(1200.0x0.6xDX51D+Z)</t>
   </si>
   <si>
-    <t>(1220.0x0.6xDX51DT+Z)</t>
-  </si>
-  <si>
     <t>(1220.0x0.7xDX51DT+Z)</t>
   </si>
   <si>
@@ -265,9 +265,6 @@
     <t>(1200.0x1.15xDX51D+Z)</t>
   </si>
   <si>
-    <t>(1200.0x1.2xDX51D+Z)</t>
-  </si>
-  <si>
     <t>(1200.0x1.25xDX51D+Z)</t>
   </si>
   <si>
@@ -277,15 +274,12 @@
     <t>(1200.0x3.0xDX51D+Z)</t>
   </si>
   <si>
-    <t>(990.0x2.5xS350GD+Z)</t>
+    <t>(1000.0x2.5xS350GD+Z)</t>
   </si>
   <si>
     <t>(1515.0x1.2xDX51D+Z)</t>
   </si>
   <si>
-    <t>(998.0x2.0xS350GD+Z)</t>
-  </si>
-  <si>
     <t>(1000.0x4.0xS350GD+Z)</t>
   </si>
   <si>
@@ -307,9 +301,6 @@
     <t>(1168.0x2.0xS350GD+Z)</t>
   </si>
   <si>
-    <t>(1170.0x4.0xS350GD+Z)</t>
-  </si>
-  <si>
     <t>(1200.0x0.5xDX51D+Z)</t>
   </si>
   <si>
@@ -322,6 +313,9 @@
     <t>(1200.0x1.75xDX51D+Z)</t>
   </si>
   <si>
+    <t>(1212.0x1.8xDX51D+Z)</t>
+  </si>
+  <si>
     <t>(1200.0x2.0xDX51D+Z)</t>
   </si>
   <si>
@@ -361,6 +355,9 @@
     <t>(1000.0x0.7xDX51DT+Z)</t>
   </si>
   <si>
+    <t>(1020.0x2.0xDD11)</t>
+  </si>
+  <si>
     <t>(1020.0x1.35xDX51D+Z)</t>
   </si>
   <si>
@@ -427,7 +424,10 @@
     <t>(1000.0x4.0x4252)</t>
   </si>
   <si>
-    <t>(985.0x2.5x4252)</t>
+    <t>(1190.0x4.0x4252)</t>
+  </si>
+  <si>
+    <t>(985.0x3.0x4252)</t>
   </si>
   <si>
     <t>(985.0x3.8x4252)</t>
@@ -439,9 +439,6 @@
     <t>(1020.0x3.0x4252)</t>
   </si>
   <si>
-    <t>(1296.0x2.6x4252)</t>
-  </si>
-  <si>
     <t>(1296.0x3.0x4252)</t>
   </si>
   <si>
@@ -529,6 +526,9 @@
     <t>(1270.0x2.5xS315MC)</t>
   </si>
   <si>
+    <t>(1296.0x2.6xS315MC)</t>
+  </si>
+  <si>
     <t>(1520.0x1.8xS315MC)</t>
   </si>
   <si>
@@ -536,9 +536,6 @@
   </si>
   <si>
     <t>(1230.0x3.8xS315MC)</t>
-  </si>
-  <si>
-    <t>(1020.0x2.0xDD11)</t>
   </si>
   <si>
     <t>(1020.0x3.0xDD11)</t>
@@ -574,8 +571,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -638,21 +635,13 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -690,7 +679,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -724,7 +713,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -759,10 +747,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -935,20 +922,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G154"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="16.1640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20.83203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="20.6640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="17.1640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.6640625" bestFit="1" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:G158"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -971,7 +949,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7">
       <c r="A2">
         <v>1072</v>
       </c>
@@ -982,19 +960,19 @@
         <v>30004224</v>
       </c>
       <c r="D2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E2">
-        <v>0.40170268005059778</v>
+        <v>0.4017026800505978</v>
       </c>
       <c r="F2" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="G2">
-        <v>0.40170268005059778</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+        <v>0.4017026800505978</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
       <c r="A3">
         <v>669</v>
       </c>
@@ -1005,19 +983,19 @@
         <v>30005768</v>
       </c>
       <c r="D3" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E3">
         <v>179.9</v>
       </c>
       <c r="F3" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="G3">
         <v>179.9</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7">
       <c r="A4">
         <v>669</v>
       </c>
@@ -1028,203 +1006,203 @@
         <v>30005768</v>
       </c>
       <c r="D4" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E4">
         <v>365.14</v>
       </c>
       <c r="F4" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="G4">
-        <v>27.594104318386371</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+        <v>103.26</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
       <c r="A5">
-        <v>669</v>
+        <v>387</v>
       </c>
       <c r="B5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C5">
-        <v>30005768</v>
+        <v>30005777</v>
       </c>
       <c r="D5" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="E5">
-        <v>4298.7884859517526</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="F5" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="G5">
-        <v>75.665895681613648</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+        <v>9.970000000000001</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
       <c r="A6">
-        <v>387</v>
+        <v>537</v>
       </c>
       <c r="B6" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C6">
         <v>30005777</v>
       </c>
       <c r="D6" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E6">
-        <v>9.9700000000000006</v>
+        <v>4.399999999999999</v>
       </c>
       <c r="F6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="G6">
-        <v>9.9700000000000006</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+        <v>3.49</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
       <c r="A7">
-        <v>470</v>
+        <v>540</v>
       </c>
       <c r="B7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C7">
         <v>30005777</v>
       </c>
       <c r="D7" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E7">
-        <v>35.363633670026204</v>
+        <v>8.66</v>
       </c>
       <c r="F7" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="G7">
-        <v>3.49</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+        <v>8.66</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
       <c r="A8">
-        <v>540</v>
+        <v>291</v>
       </c>
       <c r="B8" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C8">
-        <v>30005777</v>
+        <v>30003732</v>
       </c>
       <c r="D8" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="E8">
-        <v>8.66</v>
+        <v>17.39988157050417</v>
       </c>
       <c r="F8" t="s">
         <v>181</v>
       </c>
       <c r="G8">
-        <v>8.66</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+        <v>17.39988157050417</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
       <c r="A9">
-        <v>291</v>
+        <v>339</v>
       </c>
       <c r="B9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C9">
         <v>30003732</v>
       </c>
       <c r="D9" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E9">
-        <v>17.399881570504171</v>
+        <v>15.89776537831127</v>
       </c>
       <c r="F9" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="G9">
-        <v>17.399881570504171</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+        <v>15.89776537831127</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
       <c r="A10">
-        <v>339</v>
+        <v>475</v>
       </c>
       <c r="B10" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C10">
-        <v>30003732</v>
+        <v>30005780</v>
       </c>
       <c r="D10" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="E10">
-        <v>15.89776537831127</v>
+        <v>24.44107390333158</v>
       </c>
       <c r="F10" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="G10">
-        <v>15.89776537831127</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+        <v>2.933330635523994</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
       <c r="A11">
-        <v>475</v>
+        <v>547</v>
       </c>
       <c r="B11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C11">
         <v>30005780</v>
       </c>
       <c r="D11" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E11">
-        <v>24.441073903331581</v>
+        <v>44.546669364476</v>
       </c>
       <c r="F11" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="G11">
-        <v>2.9333306355239941</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+        <v>44.546669364476</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
       <c r="A12">
-        <v>547</v>
+        <v>287</v>
       </c>
       <c r="B12" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C12">
-        <v>30005780</v>
+        <v>30005788</v>
       </c>
       <c r="D12" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="E12">
-        <v>44.546669364476003</v>
+        <v>20</v>
       </c>
       <c r="F12" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="G12">
-        <v>44.546669364476003</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
       <c r="A13">
         <v>287</v>
       </c>
@@ -1235,88 +1213,88 @@
         <v>30005788</v>
       </c>
       <c r="D13" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E13">
-        <v>20</v>
+        <v>39.869</v>
       </c>
       <c r="F13" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="G13">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+        <v>2.719999999999999</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
       <c r="A14">
-        <v>287</v>
+        <v>654</v>
       </c>
       <c r="B14" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C14">
-        <v>30005788</v>
+        <v>30005794</v>
       </c>
       <c r="D14" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="E14">
-        <v>39.869</v>
+        <v>80.86549080624815</v>
       </c>
       <c r="F14" t="s">
         <v>181</v>
       </c>
       <c r="G14">
-        <v>2.7199999999999989</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+        <v>18.94</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
       <c r="A15">
-        <v>654</v>
+        <v>49</v>
       </c>
       <c r="B15" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C15">
-        <v>30005794</v>
+        <v>30004772</v>
       </c>
       <c r="D15" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="E15">
-        <v>80.865490806248147</v>
+        <v>21.86139023252019</v>
       </c>
       <c r="F15" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="G15">
-        <v>18.940000000000001</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+        <v>19.4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
       <c r="A16">
-        <v>49</v>
+        <v>166</v>
       </c>
       <c r="B16" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C16">
-        <v>30004772</v>
+        <v>30005804</v>
       </c>
       <c r="D16" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="E16">
-        <v>21.86139023252019</v>
+        <v>77.73899999999999</v>
       </c>
       <c r="F16" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="G16">
-        <v>19.399999999999999</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+        <v>62.54220510619895</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
       <c r="A17">
         <v>166</v>
       </c>
@@ -1327,19 +1305,19 @@
         <v>30005804</v>
       </c>
       <c r="D17" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E17">
-        <v>77.73899999999999</v>
+        <v>11007.41239757647</v>
       </c>
       <c r="F17" t="s">
         <v>181</v>
       </c>
       <c r="G17">
-        <v>65.13</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+        <v>2.587794893801046</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
       <c r="A18">
         <v>365</v>
       </c>
@@ -1350,19 +1328,19 @@
         <v>30005805</v>
       </c>
       <c r="D18" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E18">
         <v>124.4246872817084</v>
       </c>
       <c r="F18" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="G18">
-        <v>2.8350000000000009</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+        <v>2.835000000000001</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
       <c r="A19">
         <v>367</v>
       </c>
@@ -1373,19 +1351,19 @@
         <v>30005805</v>
       </c>
       <c r="D19" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E19">
         <v>12.315</v>
       </c>
       <c r="F19" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="G19">
         <v>12.315</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:7">
       <c r="A20">
         <v>532</v>
       </c>
@@ -1396,19 +1374,19 @@
         <v>30005805</v>
       </c>
       <c r="D20" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E20">
-        <v>6.6099999999999994</v>
+        <v>6.609999999999999</v>
       </c>
       <c r="F20" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="G20">
-        <v>6.6099999999999994</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+        <v>6.609999999999999</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
       <c r="A21">
         <v>445</v>
       </c>
@@ -1419,90 +1397,90 @@
         <v>30005812</v>
       </c>
       <c r="D21" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E21">
-        <v>145.61000000000001</v>
+        <v>145.61</v>
       </c>
       <c r="F21" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="G21">
-        <v>52.686222775106067</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+        <v>74.62</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
       <c r="A22">
-        <v>450</v>
+        <v>1085</v>
       </c>
       <c r="B22" t="s">
         <v>24</v>
       </c>
       <c r="C22">
-        <v>30005812</v>
+        <v>30005818</v>
       </c>
       <c r="D22" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="E22">
-        <v>26.6978978421044</v>
+        <v>34.59999999999999</v>
       </c>
       <c r="F22" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="G22">
-        <v>21.93377722489393</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+        <v>22.94</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
       <c r="A23">
-        <v>1085</v>
+        <v>708</v>
       </c>
       <c r="B23" t="s">
         <v>25</v>
       </c>
       <c r="C23">
-        <v>30005818</v>
+        <v>30005820</v>
       </c>
       <c r="D23" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="E23">
-        <v>34.599999999999987</v>
+        <v>27.05152491010099</v>
       </c>
       <c r="F23" t="s">
         <v>181</v>
       </c>
       <c r="G23">
-        <v>22.94</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
+        <v>17.14</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
       <c r="A24">
-        <v>708</v>
+        <v>188</v>
       </c>
       <c r="B24" t="s">
         <v>26</v>
       </c>
       <c r="C24">
-        <v>30005820</v>
+        <v>30003778</v>
       </c>
       <c r="D24" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="E24">
-        <v>27.051524910100991</v>
+        <v>16.21905395764419</v>
       </c>
       <c r="F24" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="G24">
-        <v>17.14</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
+        <v>16.21905395764419</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
       <c r="A25">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="B25" t="s">
         <v>27</v>
@@ -1511,21 +1489,21 @@
         <v>30003778</v>
       </c>
       <c r="D25" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E25">
-        <v>50.931070374499051</v>
+        <v>49.42534314035229</v>
       </c>
       <c r="F25" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="G25">
-        <v>50.931070374499051</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
+        <v>21.73513971156746</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
       <c r="A26">
-        <v>383</v>
+        <v>196</v>
       </c>
       <c r="B26" t="s">
         <v>28</v>
@@ -1534,464 +1512,464 @@
         <v>30003778</v>
       </c>
       <c r="D26" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E26">
-        <v>16.444379407323051</v>
+        <v>7.869621555078039</v>
       </c>
       <c r="F26" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="G26">
-        <v>15.428929625500951</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
+        <v>7.869621555078039</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
       <c r="A27">
-        <v>850</v>
+        <v>380</v>
       </c>
       <c r="B27" t="s">
         <v>29</v>
       </c>
       <c r="C27">
-        <v>30005842</v>
+        <v>30003778</v>
       </c>
       <c r="D27" t="s">
-        <v>29</v>
+        <v>134</v>
       </c>
       <c r="E27">
-        <v>18.251168380980911</v>
+        <v>10.74875139230171</v>
       </c>
       <c r="F27" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="G27">
-        <v>18.251168380980911</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
+        <v>10.74875139230171</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
       <c r="A28">
-        <v>1176</v>
+        <v>457</v>
       </c>
       <c r="B28" t="s">
         <v>30</v>
       </c>
       <c r="C28">
-        <v>30005848</v>
+        <v>30003778</v>
       </c>
       <c r="D28" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E28">
-        <v>76.230221018753895</v>
+        <v>9.787433383408596</v>
       </c>
       <c r="F28" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="G28">
-        <v>18.760000000000002</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+        <v>9.787433383408596</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
       <c r="A29">
-        <v>520</v>
+        <v>850</v>
       </c>
       <c r="B29" t="s">
         <v>31</v>
       </c>
       <c r="C29">
-        <v>30005855</v>
+        <v>30005842</v>
       </c>
       <c r="D29" t="s">
-        <v>134</v>
+        <v>31</v>
       </c>
       <c r="E29">
-        <v>30.715529014303851</v>
+        <v>18.25116838098091</v>
       </c>
       <c r="F29" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="G29">
-        <v>30.715529014303851</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+        <v>18.25116838098091</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
       <c r="A30">
-        <v>1165</v>
+        <v>1176</v>
       </c>
       <c r="B30" t="s">
         <v>32</v>
       </c>
       <c r="C30">
-        <v>30005859</v>
+        <v>30005848</v>
       </c>
       <c r="D30" t="s">
         <v>135</v>
       </c>
       <c r="E30">
-        <v>37.78634104814563</v>
+        <v>76.23022101875389</v>
       </c>
       <c r="F30" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="G30">
-        <v>37.78634104814563</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+        <v>18.76</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
       <c r="A31">
-        <v>1053</v>
+        <v>1185</v>
       </c>
       <c r="B31" t="s">
         <v>33</v>
       </c>
       <c r="C31">
-        <v>30005862</v>
+        <v>30005851</v>
       </c>
       <c r="D31" t="s">
         <v>136</v>
       </c>
       <c r="E31">
-        <v>79.98308176037736</v>
+        <v>8.301023980604819</v>
       </c>
       <c r="F31" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="G31">
-        <v>25.363081760377359</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+        <v>8.301023980604819</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7">
       <c r="A32">
-        <v>527</v>
+        <v>520</v>
       </c>
       <c r="B32" t="s">
         <v>34</v>
       </c>
       <c r="C32">
-        <v>30005864</v>
+        <v>30005857</v>
       </c>
       <c r="D32" t="s">
         <v>137</v>
       </c>
       <c r="E32">
-        <v>255.8854095561428</v>
+        <v>30.71552901430385</v>
       </c>
       <c r="F32" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="G32">
-        <v>64.55</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+        <v>30.71552901430385</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7">
       <c r="A33">
-        <v>985</v>
+        <v>1165</v>
       </c>
       <c r="B33" t="s">
         <v>35</v>
       </c>
       <c r="C33">
-        <v>30005872</v>
+        <v>30005859</v>
       </c>
       <c r="D33" t="s">
         <v>138</v>
       </c>
       <c r="E33">
-        <v>30.229072838516501</v>
+        <v>37.78634104814563</v>
       </c>
       <c r="F33" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="G33">
-        <v>27.48</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+        <v>37.78634104814563</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7">
       <c r="A34">
-        <v>985</v>
+        <v>1053</v>
       </c>
       <c r="B34" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C34">
-        <v>30005873</v>
+        <v>30005862</v>
       </c>
       <c r="D34" t="s">
         <v>139</v>
       </c>
       <c r="E34">
-        <v>30.229072838516501</v>
+        <v>79.98308176037736</v>
       </c>
       <c r="F34" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="G34">
-        <v>2.7490728385165011</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+        <v>25.36308176037736</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7">
       <c r="A35">
-        <v>207</v>
+        <v>527</v>
       </c>
       <c r="B35" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C35">
-        <v>30005886</v>
+        <v>30005864</v>
       </c>
       <c r="D35" t="s">
         <v>140</v>
       </c>
       <c r="E35">
-        <v>317.42338067961879</v>
+        <v>255.8854095561428</v>
       </c>
       <c r="F35" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="G35">
-        <v>23.44</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+        <v>64.55</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7">
       <c r="A36">
-        <v>1224</v>
+        <v>985</v>
       </c>
       <c r="B36" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C36">
-        <v>30003956</v>
+        <v>30005873</v>
       </c>
       <c r="D36" t="s">
         <v>141</v>
       </c>
       <c r="E36">
-        <v>7.7363753830595083</v>
+        <v>30.2290728385165</v>
       </c>
       <c r="F36" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="G36">
-        <v>7.7363753830595083</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+        <v>27.35</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7">
       <c r="A37">
-        <v>781</v>
+        <v>285</v>
       </c>
       <c r="B37" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C37">
-        <v>30001483</v>
+        <v>30005886</v>
       </c>
       <c r="D37" t="s">
         <v>142</v>
       </c>
       <c r="E37">
-        <v>1.5607082513080299</v>
+        <v>94.27210005885379</v>
       </c>
       <c r="F37" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="G37">
-        <v>1.5607082513080299</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+        <v>23.44</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7">
       <c r="A38">
-        <v>369</v>
+        <v>1224</v>
       </c>
       <c r="B38" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C38">
-        <v>30003535</v>
+        <v>30003956</v>
       </c>
       <c r="D38" t="s">
         <v>143</v>
       </c>
       <c r="E38">
-        <v>4.0299999999999976</v>
+        <v>7.736375383059508</v>
       </c>
       <c r="F38" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="G38">
-        <v>4.0299999999999976</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+        <v>7.736375383059508</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7">
       <c r="A39">
-        <v>418</v>
+        <v>781</v>
       </c>
       <c r="B39" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C39">
-        <v>30003535</v>
+        <v>30001483</v>
       </c>
       <c r="D39" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E39">
-        <v>40</v>
+        <v>1.56070825130803</v>
       </c>
       <c r="F39" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="G39">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
+        <v>1.56070825130803</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
       <c r="A40">
-        <v>445</v>
+        <v>369</v>
       </c>
       <c r="B40" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="C40">
         <v>30003535</v>
       </c>
       <c r="D40" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="E40">
-        <v>22.78</v>
+        <v>4.029999999999998</v>
       </c>
       <c r="F40" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="G40">
-        <v>22.78</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
+        <v>4.029999999999998</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
       <c r="A41">
-        <v>445</v>
+        <v>418</v>
       </c>
       <c r="B41" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="C41">
         <v>30003535</v>
       </c>
       <c r="D41" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="E41">
-        <v>145.61000000000001</v>
+        <v>40</v>
       </c>
       <c r="F41" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="G41">
-        <v>65.52000000000001</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7">
       <c r="A42">
-        <v>524</v>
+        <v>445</v>
       </c>
       <c r="B42" t="s">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="C42">
         <v>30003535</v>
       </c>
       <c r="D42" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="E42">
-        <v>49.82</v>
+        <v>22.78</v>
       </c>
       <c r="F42" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="G42">
-        <v>15.52</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
+        <v>22.78</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7">
       <c r="A43">
-        <v>928</v>
+        <v>445</v>
       </c>
       <c r="B43" t="s">
-        <v>42</v>
+        <v>23</v>
       </c>
       <c r="C43">
         <v>30003535</v>
       </c>
       <c r="D43" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="E43">
-        <v>1.4499999999999991</v>
+        <v>145.61</v>
       </c>
       <c r="F43" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="G43">
-        <v>1.4499999999999991</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
+        <v>65.52000000000001</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7">
       <c r="A44">
-        <v>779</v>
+        <v>524</v>
       </c>
       <c r="B44" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C44">
-        <v>30003536</v>
+        <v>30003535</v>
       </c>
       <c r="D44" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E44">
-        <v>50</v>
+        <v>49.82</v>
       </c>
       <c r="F44" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="G44">
-        <v>18.5</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
+        <v>15.52</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7">
       <c r="A45">
-        <v>369</v>
+        <v>928</v>
       </c>
       <c r="B45" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="C45">
-        <v>30003537</v>
+        <v>30003535</v>
       </c>
       <c r="D45" t="s">
         <v>145</v>
       </c>
       <c r="E45">
-        <v>29.04</v>
+        <v>1.449999999999999</v>
       </c>
       <c r="F45" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="G45">
-        <v>7.7</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
+        <v>1.449999999999999</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7">
       <c r="A46">
         <v>779</v>
       </c>
       <c r="B46" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="C46">
-        <v>30003543</v>
+        <v>30003536</v>
       </c>
       <c r="D46" t="s">
         <v>146</v>
@@ -2000,1142 +1978,1142 @@
         <v>50</v>
       </c>
       <c r="F46" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="G46">
-        <v>31.5</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
+        <v>18.5</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7">
       <c r="A47">
+        <v>369</v>
+      </c>
+      <c r="B47" t="s">
+        <v>42</v>
+      </c>
+      <c r="C47">
+        <v>30003537</v>
+      </c>
+      <c r="D47" t="s">
+        <v>147</v>
+      </c>
+      <c r="E47">
+        <v>29.04</v>
+      </c>
+      <c r="F47" t="s">
+        <v>183</v>
+      </c>
+      <c r="G47">
+        <v>7.7</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7">
+      <c r="A48">
         <v>779</v>
       </c>
-      <c r="B47" t="s">
-        <v>43</v>
-      </c>
-      <c r="C47">
-        <v>30003543</v>
-      </c>
-      <c r="D47" t="s">
-        <v>146</v>
-      </c>
-      <c r="E47">
-        <v>164.68</v>
-      </c>
-      <c r="F47" t="s">
-        <v>181</v>
-      </c>
-      <c r="G47">
-        <v>164.68</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A48">
-        <v>1187</v>
-      </c>
       <c r="B48" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C48">
         <v>30003543</v>
       </c>
       <c r="D48" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E48">
-        <v>3.7100000000000009</v>
+        <v>50</v>
       </c>
       <c r="F48" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="G48">
-        <v>3.7100000000000009</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
+        <v>31.5</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7">
       <c r="A49">
-        <v>1187</v>
+        <v>779</v>
       </c>
       <c r="B49" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C49">
         <v>30003543</v>
       </c>
       <c r="D49" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E49">
-        <v>138.85523659701769</v>
+        <v>164.68</v>
       </c>
       <c r="F49" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="G49">
+        <v>164.68</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7">
+      <c r="A50">
+        <v>1187</v>
+      </c>
+      <c r="B50" t="s">
+        <v>47</v>
+      </c>
+      <c r="C50">
+        <v>30003543</v>
+      </c>
+      <c r="D50" t="s">
+        <v>148</v>
+      </c>
+      <c r="E50">
+        <v>3.710000000000001</v>
+      </c>
+      <c r="F50" t="s">
+        <v>182</v>
+      </c>
+      <c r="G50">
+        <v>3.710000000000001</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7">
+      <c r="A51">
+        <v>1187</v>
+      </c>
+      <c r="B51" t="s">
+        <v>47</v>
+      </c>
+      <c r="C51">
+        <v>30003543</v>
+      </c>
+      <c r="D51" t="s">
+        <v>148</v>
+      </c>
+      <c r="E51">
+        <v>138.8552365970177</v>
+      </c>
+      <c r="F51" t="s">
+        <v>181</v>
+      </c>
+      <c r="G51">
         <v>69.53</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A50">
+    <row r="52" spans="1:7">
+      <c r="A52">
         <v>79</v>
       </c>
-      <c r="B50" t="s">
-        <v>45</v>
-      </c>
-      <c r="C50">
-        <v>30003546</v>
-      </c>
-      <c r="D50" t="s">
-        <v>147</v>
-      </c>
-      <c r="E50">
-        <v>20</v>
-      </c>
-      <c r="F50" t="s">
-        <v>181</v>
-      </c>
-      <c r="G50">
-        <v>7.7220000000000164</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A51">
-        <v>159</v>
-      </c>
-      <c r="B51" t="s">
-        <v>46</v>
-      </c>
-      <c r="C51">
-        <v>30003546</v>
-      </c>
-      <c r="D51" t="s">
-        <v>147</v>
-      </c>
-      <c r="E51">
-        <v>0.55800000000000005</v>
-      </c>
-      <c r="F51" t="s">
-        <v>181</v>
-      </c>
-      <c r="G51">
-        <v>0.55800000000000005</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A52">
-        <v>407</v>
-      </c>
       <c r="B52" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C52">
         <v>30003546</v>
       </c>
       <c r="D52" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="E52">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="F52" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="G52">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.2">
+        <v>7.722000000000016</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7">
       <c r="A53">
-        <v>427</v>
+        <v>159</v>
       </c>
       <c r="B53" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C53">
         <v>30003546</v>
       </c>
       <c r="D53" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="E53">
-        <v>38.44</v>
+        <v>0.5580000000000001</v>
       </c>
       <c r="F53" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="G53">
-        <v>26.249999999999989</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.2">
+        <v>0.5580000000000001</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7">
       <c r="A54">
-        <v>825</v>
+        <v>407</v>
       </c>
       <c r="B54" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C54">
         <v>30003546</v>
       </c>
       <c r="D54" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="E54">
+        <v>25</v>
+      </c>
+      <c r="F54" t="s">
+        <v>182</v>
+      </c>
+      <c r="G54">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7">
+      <c r="A55">
+        <v>427</v>
+      </c>
+      <c r="B55" t="s">
+        <v>51</v>
+      </c>
+      <c r="C55">
+        <v>30003546</v>
+      </c>
+      <c r="D55" t="s">
+        <v>149</v>
+      </c>
+      <c r="E55">
+        <v>38.44</v>
+      </c>
+      <c r="F55" t="s">
+        <v>182</v>
+      </c>
+      <c r="G55">
+        <v>26.24999999999999</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7">
+      <c r="A56">
+        <v>825</v>
+      </c>
+      <c r="B56" t="s">
+        <v>52</v>
+      </c>
+      <c r="C56">
+        <v>30003546</v>
+      </c>
+      <c r="D56" t="s">
+        <v>149</v>
+      </c>
+      <c r="E56">
         <v>128</v>
       </c>
-      <c r="F54" t="s">
-        <v>180</v>
-      </c>
-      <c r="G54">
-        <v>11.400000000000009</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A55">
+      <c r="F56" t="s">
+        <v>182</v>
+      </c>
+      <c r="G56">
+        <v>11.40000000000001</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7">
+      <c r="A57">
         <v>389</v>
       </c>
-      <c r="B55" t="s">
-        <v>50</v>
-      </c>
-      <c r="C55">
+      <c r="B57" t="s">
+        <v>53</v>
+      </c>
+      <c r="C57">
         <v>30003547</v>
       </c>
-      <c r="D55" t="s">
-        <v>148</v>
-      </c>
-      <c r="E55">
-        <v>80.569999999999993</v>
-      </c>
-      <c r="F55" t="s">
-        <v>180</v>
-      </c>
-      <c r="G55">
-        <v>80.569999999999993</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A56">
+      <c r="D57" t="s">
+        <v>150</v>
+      </c>
+      <c r="E57">
+        <v>80.56999999999999</v>
+      </c>
+      <c r="F57" t="s">
+        <v>182</v>
+      </c>
+      <c r="G57">
+        <v>80.56999999999999</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7">
+      <c r="A58">
         <v>427</v>
       </c>
-      <c r="B56" t="s">
-        <v>48</v>
-      </c>
-      <c r="C56">
+      <c r="B58" t="s">
+        <v>51</v>
+      </c>
+      <c r="C58">
         <v>30003547</v>
       </c>
-      <c r="D56" t="s">
-        <v>148</v>
-      </c>
-      <c r="E56">
+      <c r="D58" t="s">
+        <v>150</v>
+      </c>
+      <c r="E58">
         <v>38.44</v>
       </c>
-      <c r="F56" t="s">
-        <v>180</v>
-      </c>
-      <c r="G56">
+      <c r="F58" t="s">
+        <v>182</v>
+      </c>
+      <c r="G58">
         <v>12.19000000000001</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A57">
+    <row r="59" spans="1:7">
+      <c r="A59">
         <v>487</v>
       </c>
-      <c r="B57" t="s">
-        <v>51</v>
-      </c>
-      <c r="C57">
-        <v>30003550</v>
-      </c>
-      <c r="D57" t="s">
-        <v>149</v>
-      </c>
-      <c r="E57">
-        <v>71.790000000000006</v>
-      </c>
-      <c r="F57" t="s">
-        <v>181</v>
-      </c>
-      <c r="G57">
-        <v>71.790000000000006</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A58">
-        <v>554</v>
-      </c>
-      <c r="B58" t="s">
-        <v>52</v>
-      </c>
-      <c r="C58">
-        <v>30003550</v>
-      </c>
-      <c r="D58" t="s">
-        <v>149</v>
-      </c>
-      <c r="E58">
-        <v>158</v>
-      </c>
-      <c r="F58" t="s">
-        <v>180</v>
-      </c>
-      <c r="G58">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A59">
-        <v>554</v>
-      </c>
       <c r="B59" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C59">
         <v>30003550</v>
       </c>
       <c r="D59" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="E59">
-        <v>74.16</v>
+        <v>71.79000000000001</v>
       </c>
       <c r="F59" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="G59">
-        <v>74.16</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.2">
+        <v>71.79000000000001</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7">
       <c r="A60">
-        <v>614</v>
+        <v>554</v>
       </c>
       <c r="B60" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C60">
         <v>30003550</v>
       </c>
       <c r="D60" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="E60">
-        <v>4.2700000000000031</v>
+        <v>158</v>
       </c>
       <c r="F60" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="G60">
-        <v>4.2700000000000031</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.2">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7">
       <c r="A61">
-        <v>617</v>
+        <v>554</v>
       </c>
       <c r="B61" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C61">
         <v>30003550</v>
       </c>
       <c r="D61" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="E61">
-        <v>38.32</v>
+        <v>74.16</v>
       </c>
       <c r="F61" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="G61">
-        <v>33.619999999999997</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.2">
+        <v>74.16</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7">
       <c r="A62">
-        <v>621</v>
+        <v>614</v>
       </c>
       <c r="B62" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C62">
         <v>30003550</v>
       </c>
       <c r="D62" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="E62">
-        <v>4.9999999999997158E-2</v>
+        <v>4.270000000000003</v>
       </c>
       <c r="F62" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="G62">
-        <v>4.9999999999997158E-2</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.2">
+        <v>4.270000000000003</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7">
       <c r="A63">
-        <v>656</v>
+        <v>617</v>
       </c>
       <c r="B63" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C63">
         <v>30003550</v>
       </c>
       <c r="D63" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="E63">
-        <v>29.18</v>
+        <v>38.32</v>
       </c>
       <c r="F63" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="G63">
-        <v>29.18</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.2">
+        <v>33.62</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7">
       <c r="A64">
-        <v>656</v>
+        <v>621</v>
       </c>
       <c r="B64" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C64">
         <v>30003550</v>
       </c>
       <c r="D64" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="E64">
-        <v>1.01</v>
+        <v>0.04999999999999716</v>
       </c>
       <c r="F64" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="G64">
-        <v>1.01</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.2">
+        <v>0.04999999999999716</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7">
       <c r="A65">
-        <v>669</v>
+        <v>656</v>
       </c>
       <c r="B65" t="s">
-        <v>8</v>
+        <v>59</v>
       </c>
       <c r="C65">
         <v>30003550</v>
       </c>
       <c r="D65" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="E65">
-        <v>365.14</v>
+        <v>29.18</v>
       </c>
       <c r="F65" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="G65">
-        <v>337.54589568161367</v>
-      </c>
-    </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.2">
+        <v>29.18</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7">
       <c r="A66">
-        <v>845</v>
+        <v>656</v>
       </c>
       <c r="B66" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C66">
         <v>30003550</v>
       </c>
       <c r="D66" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="E66">
-        <v>14.191000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="F66" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="G66">
-        <v>14.191000000000001</v>
-      </c>
-    </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.2">
+        <v>1.01</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7">
       <c r="A67">
-        <v>1100</v>
+        <v>669</v>
       </c>
       <c r="B67" t="s">
-        <v>58</v>
+        <v>8</v>
       </c>
       <c r="C67">
         <v>30003550</v>
       </c>
       <c r="D67" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="E67">
-        <v>36.068104318386403</v>
+        <v>365.14</v>
       </c>
       <c r="F67" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="G67">
-        <v>36.068104318386403</v>
-      </c>
-    </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.2">
+        <v>261.88</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7">
       <c r="A68">
-        <v>1101</v>
+        <v>673</v>
       </c>
       <c r="B68" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C68">
         <v>30003550</v>
       </c>
       <c r="D68" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="E68">
-        <v>1.3449999999999971</v>
+        <v>256.8530825408739</v>
       </c>
       <c r="F68" t="s">
         <v>181</v>
       </c>
       <c r="G68">
-        <v>1.3449999999999971</v>
-      </c>
-    </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.2">
+        <v>111.734</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7">
       <c r="A69">
+        <v>845</v>
+      </c>
+      <c r="B69" t="s">
+        <v>61</v>
+      </c>
+      <c r="C69">
+        <v>30003550</v>
+      </c>
+      <c r="D69" t="s">
+        <v>151</v>
+      </c>
+      <c r="E69">
+        <v>14.191</v>
+      </c>
+      <c r="F69" t="s">
+        <v>183</v>
+      </c>
+      <c r="G69">
+        <v>14.191</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7">
+      <c r="A70">
+        <v>1101</v>
+      </c>
+      <c r="B70" t="s">
+        <v>62</v>
+      </c>
+      <c r="C70">
+        <v>30003550</v>
+      </c>
+      <c r="D70" t="s">
+        <v>151</v>
+      </c>
+      <c r="E70">
+        <v>1.344999999999997</v>
+      </c>
+      <c r="F70" t="s">
+        <v>183</v>
+      </c>
+      <c r="G70">
+        <v>1.344999999999997</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7">
+      <c r="A71">
         <v>617</v>
       </c>
-      <c r="B69" t="s">
-        <v>54</v>
-      </c>
-      <c r="C69">
+      <c r="B71" t="s">
+        <v>57</v>
+      </c>
+      <c r="C71">
         <v>30003551</v>
       </c>
-      <c r="D69" t="s">
-        <v>150</v>
-      </c>
-      <c r="E69">
+      <c r="D71" t="s">
+        <v>152</v>
+      </c>
+      <c r="E71">
         <v>38.32</v>
       </c>
-      <c r="F69" t="s">
-        <v>180</v>
-      </c>
-      <c r="G69">
-        <v>4.6999999999999993</v>
-      </c>
-    </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A70">
+      <c r="F71" t="s">
+        <v>182</v>
+      </c>
+      <c r="G71">
+        <v>4.699999999999999</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7">
+      <c r="A72">
         <v>845</v>
-      </c>
-      <c r="B70" t="s">
-        <v>57</v>
-      </c>
-      <c r="C70">
-        <v>30003551</v>
-      </c>
-      <c r="D70" t="s">
-        <v>150</v>
-      </c>
-      <c r="E70">
-        <v>20</v>
-      </c>
-      <c r="F70" t="s">
-        <v>180</v>
-      </c>
-      <c r="G70">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A71">
-        <v>1</v>
-      </c>
-      <c r="B71" t="s">
-        <v>60</v>
-      </c>
-      <c r="C71">
-        <v>30003555</v>
-      </c>
-      <c r="D71" t="s">
-        <v>151</v>
-      </c>
-      <c r="E71">
-        <v>20</v>
-      </c>
-      <c r="F71" t="s">
-        <v>181</v>
-      </c>
-      <c r="G71">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A72">
-        <v>41</v>
       </c>
       <c r="B72" t="s">
         <v>61</v>
       </c>
       <c r="C72">
-        <v>30003555</v>
+        <v>30003551</v>
       </c>
       <c r="D72" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E72">
-        <v>235</v>
+        <v>20</v>
       </c>
       <c r="F72" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="G72">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7">
       <c r="A73">
-        <v>64</v>
+        <v>1</v>
       </c>
       <c r="B73" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C73">
         <v>30003555</v>
       </c>
       <c r="D73" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="E73">
-        <v>9.51</v>
+        <v>20</v>
       </c>
       <c r="F73" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="G73">
-        <v>9.51</v>
-      </c>
-    </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7">
       <c r="A74">
-        <v>88</v>
+        <v>41</v>
       </c>
       <c r="B74" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C74">
         <v>30003555</v>
       </c>
       <c r="D74" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="E74">
-        <v>80</v>
+        <v>235</v>
       </c>
       <c r="F74" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="G74">
-        <v>48.740999999999872</v>
-      </c>
-    </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.2">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7">
       <c r="A75">
-        <v>165</v>
+        <v>64</v>
       </c>
       <c r="B75" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C75">
         <v>30003555</v>
       </c>
       <c r="D75" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="E75">
-        <v>2.629999999999999</v>
+        <v>9.51</v>
       </c>
       <c r="F75" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="G75">
-        <v>2.629999999999999</v>
-      </c>
-    </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.2">
+        <v>9.51</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7">
       <c r="A76">
-        <v>165</v>
+        <v>88</v>
       </c>
       <c r="B76" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C76">
         <v>30003555</v>
       </c>
       <c r="D76" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="E76">
-        <v>194.39</v>
+        <v>80</v>
       </c>
       <c r="F76" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="G76">
-        <v>194.39</v>
-      </c>
-    </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.2">
+        <v>30.58168750733455</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7">
       <c r="A77">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B77" t="s">
-        <v>19</v>
+        <v>67</v>
       </c>
       <c r="C77">
         <v>30003555</v>
       </c>
       <c r="D77" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="E77">
-        <v>77.73899999999999</v>
+        <v>2.629999999999999</v>
       </c>
       <c r="F77" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="G77">
-        <v>12.608999999999989</v>
-      </c>
-    </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.2">
+        <v>2.629999999999999</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7">
       <c r="A78">
-        <v>320</v>
+        <v>165</v>
       </c>
       <c r="B78" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C78">
         <v>30003555</v>
       </c>
       <c r="D78" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="E78">
-        <v>20</v>
+        <v>194.39</v>
       </c>
       <c r="F78" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="G78">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.2">
+        <v>194.39</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7">
       <c r="A79">
-        <v>320</v>
+        <v>166</v>
       </c>
       <c r="B79" t="s">
-        <v>65</v>
+        <v>19</v>
       </c>
       <c r="C79">
         <v>30003555</v>
       </c>
       <c r="D79" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="E79">
-        <v>47.33</v>
+        <v>77.73899999999999</v>
       </c>
       <c r="F79" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="G79">
-        <v>47.33</v>
-      </c>
-    </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.2">
+        <v>15.19679489380104</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7">
       <c r="A80">
-        <v>711</v>
+        <v>304</v>
       </c>
       <c r="B80" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C80">
         <v>30003555</v>
       </c>
       <c r="D80" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="E80">
-        <v>87.34</v>
+        <v>15.57151759886431</v>
       </c>
       <c r="F80" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="G80">
-        <v>87.34</v>
-      </c>
-    </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.2">
+        <v>15.57151759886431</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7">
       <c r="A81">
-        <v>74</v>
+        <v>320</v>
       </c>
       <c r="B81" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C81">
-        <v>30003563</v>
+        <v>30003555</v>
       </c>
       <c r="D81" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E81">
         <v>20</v>
       </c>
       <c r="F81" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="G81">
         <v>20</v>
       </c>
     </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:7">
       <c r="A82">
-        <v>105</v>
+        <v>320</v>
       </c>
       <c r="B82" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C82">
-        <v>30003563</v>
+        <v>30003555</v>
       </c>
       <c r="D82" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E82">
-        <v>25</v>
+        <v>47.33</v>
       </c>
       <c r="F82" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="G82">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.2">
+        <v>47.33</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7">
       <c r="A83">
-        <v>281</v>
+        <v>711</v>
       </c>
       <c r="B83" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C83">
-        <v>30003563</v>
+        <v>30003555</v>
       </c>
       <c r="D83" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E83">
-        <v>3.230000000000004</v>
+        <v>87.34</v>
       </c>
       <c r="F83" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="G83">
-        <v>3.230000000000004</v>
-      </c>
-    </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.2">
+        <v>87.34</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7">
       <c r="A84">
-        <v>285</v>
+        <v>74</v>
       </c>
       <c r="B84" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C84">
         <v>30003563</v>
       </c>
       <c r="D84" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E84">
-        <v>33.71</v>
+        <v>20</v>
       </c>
       <c r="F84" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="G84">
-        <v>33.71</v>
-      </c>
-    </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7">
       <c r="A85">
-        <v>332</v>
+        <v>105</v>
       </c>
       <c r="B85" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C85">
         <v>30003563</v>
       </c>
       <c r="D85" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E85">
-        <v>170.14809082647</v>
+        <v>25</v>
       </c>
       <c r="F85" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="G85">
-        <v>52.58</v>
-      </c>
-    </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.2">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7">
       <c r="A86">
-        <v>1228</v>
+        <v>281</v>
       </c>
       <c r="B86" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C86">
-        <v>30004110</v>
+        <v>30003563</v>
       </c>
       <c r="D86" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E86">
-        <v>0.54154700850589432</v>
+        <v>3.230000000000004</v>
       </c>
       <c r="F86" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="G86">
-        <v>0.54154700850589432</v>
-      </c>
-    </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.2">
+        <v>3.230000000000004</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7">
       <c r="A87">
-        <v>526</v>
+        <v>285</v>
       </c>
       <c r="B87" t="s">
-        <v>73</v>
+        <v>39</v>
       </c>
       <c r="C87">
-        <v>30005704</v>
+        <v>30003563</v>
       </c>
       <c r="D87" t="s">
         <v>154</v>
       </c>
       <c r="E87">
-        <v>191.01779245000671</v>
+        <v>33.71</v>
       </c>
       <c r="F87" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="G87">
-        <v>134.58000000000001</v>
-      </c>
-    </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.2">
+        <v>33.71</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7">
       <c r="A88">
-        <v>1176</v>
+        <v>332</v>
       </c>
       <c r="B88" t="s">
-        <v>30</v>
+        <v>74</v>
       </c>
       <c r="C88">
-        <v>30005707</v>
+        <v>30003563</v>
       </c>
       <c r="D88" t="s">
+        <v>154</v>
+      </c>
+      <c r="E88">
+        <v>170.14809082647</v>
+      </c>
+      <c r="F88" t="s">
+        <v>181</v>
+      </c>
+      <c r="G88">
+        <v>52.58</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7">
+      <c r="A89">
+        <v>1228</v>
+      </c>
+      <c r="B89" t="s">
+        <v>75</v>
+      </c>
+      <c r="C89">
+        <v>30004110</v>
+      </c>
+      <c r="D89" t="s">
         <v>155</v>
       </c>
-      <c r="E88">
-        <v>76.230221018753895</v>
-      </c>
-      <c r="F88" t="s">
-        <v>179</v>
-      </c>
-      <c r="G88">
-        <v>53.52</v>
-      </c>
-    </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A89">
-        <v>268</v>
-      </c>
-      <c r="B89" t="s">
-        <v>74</v>
-      </c>
-      <c r="C89">
-        <v>30003660</v>
-      </c>
-      <c r="D89" t="s">
-        <v>156</v>
-      </c>
       <c r="E89">
-        <v>6.1399999999999988</v>
+        <v>0.5415470085058943</v>
       </c>
       <c r="F89" t="s">
         <v>181</v>
       </c>
       <c r="G89">
-        <v>6.1399999999999988</v>
-      </c>
-    </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.2">
+        <v>0.5415470085058943</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7">
       <c r="A90">
-        <v>385</v>
+        <v>526</v>
       </c>
       <c r="B90" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C90">
-        <v>30003660</v>
+        <v>30005704</v>
       </c>
       <c r="D90" t="s">
         <v>156</v>
       </c>
       <c r="E90">
-        <v>1021.295054817586</v>
+        <v>191.0177924500067</v>
       </c>
       <c r="F90" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="G90">
-        <v>472.28</v>
-      </c>
-    </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.2">
+        <v>134.58</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7">
       <c r="A91">
-        <v>487</v>
+        <v>1176</v>
       </c>
       <c r="B91" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="C91">
+        <v>30005707</v>
+      </c>
+      <c r="D91" t="s">
+        <v>157</v>
+      </c>
+      <c r="E91">
+        <v>76.23022101875389</v>
+      </c>
+      <c r="F91" t="s">
+        <v>181</v>
+      </c>
+      <c r="G91">
+        <v>53.52</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7">
+      <c r="A92">
+        <v>268</v>
+      </c>
+      <c r="B92" t="s">
+        <v>77</v>
+      </c>
+      <c r="C92">
         <v>30003660</v>
       </c>
-      <c r="D91" t="s">
-        <v>156</v>
-      </c>
-      <c r="E91">
-        <v>148</v>
-      </c>
-      <c r="F91" t="s">
-        <v>180</v>
-      </c>
-      <c r="G91">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A92">
-        <v>1053</v>
-      </c>
-      <c r="B92" t="s">
-        <v>33</v>
-      </c>
-      <c r="C92">
-        <v>30005708</v>
-      </c>
       <c r="D92" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E92">
-        <v>79.98308176037736</v>
+        <v>6.139999999999999</v>
       </c>
       <c r="F92" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="G92">
-        <v>54.62</v>
-      </c>
-    </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.2">
+        <v>6.139999999999999</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7">
       <c r="A93">
-        <v>282</v>
+        <v>385</v>
       </c>
       <c r="B93" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C93">
-        <v>30003662</v>
+        <v>30003660</v>
       </c>
       <c r="D93" t="s">
         <v>158</v>
       </c>
       <c r="E93">
-        <v>0.77999999999999936</v>
+        <v>1021.295054817586</v>
       </c>
       <c r="F93" t="s">
         <v>181</v>
       </c>
       <c r="G93">
-        <v>0.77999999999999936</v>
-      </c>
-    </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.2">
+        <v>472.28</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7">
       <c r="A94">
-        <v>462</v>
+        <v>487</v>
       </c>
       <c r="B94" t="s">
-        <v>77</v>
+        <v>54</v>
       </c>
       <c r="C94">
-        <v>30003662</v>
+        <v>30003660</v>
       </c>
       <c r="D94" t="s">
         <v>158</v>
       </c>
       <c r="E94">
-        <v>12.92</v>
+        <v>148</v>
       </c>
       <c r="F94" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="G94">
-        <v>12.92</v>
-      </c>
-    </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.2">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7">
       <c r="A95">
-        <v>466</v>
+        <v>1053</v>
       </c>
       <c r="B95" t="s">
-        <v>78</v>
+        <v>36</v>
       </c>
       <c r="C95">
-        <v>30003662</v>
+        <v>30005708</v>
       </c>
       <c r="D95" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E95">
-        <v>8.1700000000000017</v>
+        <v>79.98308176037736</v>
       </c>
       <c r="F95" t="s">
         <v>181</v>
       </c>
       <c r="G95">
-        <v>8.1700000000000017</v>
-      </c>
-    </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.2">
+        <v>54.62</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7">
       <c r="A96">
-        <v>507</v>
+        <v>282</v>
       </c>
       <c r="B96" t="s">
         <v>79</v>
@@ -3144,21 +3122,21 @@
         <v>30003662</v>
       </c>
       <c r="D96" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="E96">
-        <v>3.6900000000000008</v>
+        <v>0.7799999999999994</v>
       </c>
       <c r="F96" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="G96">
-        <v>3.6900000000000008</v>
-      </c>
-    </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.2">
+        <v>0.7799999999999994</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7">
       <c r="A97">
-        <v>537</v>
+        <v>462</v>
       </c>
       <c r="B97" t="s">
         <v>80</v>
@@ -3167,21 +3145,21 @@
         <v>30003662</v>
       </c>
       <c r="D97" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="E97">
-        <v>4.3999999999999986</v>
+        <v>12.92</v>
       </c>
       <c r="F97" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="G97">
-        <v>4.3999999999999986</v>
-      </c>
-    </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.2">
+        <v>12.92</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7">
       <c r="A98">
-        <v>573</v>
+        <v>466</v>
       </c>
       <c r="B98" t="s">
         <v>81</v>
@@ -3190,21 +3168,21 @@
         <v>30003662</v>
       </c>
       <c r="D98" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="E98">
-        <v>40.667927562236372</v>
+        <v>8.170000000000002</v>
       </c>
       <c r="F98" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="G98">
-        <v>40.667927562236372</v>
-      </c>
-    </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.2">
+        <v>8.170000000000002</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7">
       <c r="A99">
-        <v>637</v>
+        <v>507</v>
       </c>
       <c r="B99" t="s">
         <v>82</v>
@@ -3213,44 +3191,44 @@
         <v>30003662</v>
       </c>
       <c r="D99" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="E99">
-        <v>120</v>
+        <v>3.690000000000001</v>
       </c>
       <c r="F99" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="G99">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.2">
+        <v>3.690000000000001</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7">
       <c r="A100">
-        <v>637</v>
+        <v>537</v>
       </c>
       <c r="B100" t="s">
-        <v>82</v>
+        <v>10</v>
       </c>
       <c r="C100">
         <v>30003662</v>
       </c>
       <c r="D100" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="E100">
-        <v>260.62</v>
+        <v>4.399999999999999</v>
       </c>
       <c r="F100" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="G100">
-        <v>260.62</v>
-      </c>
-    </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.2">
+        <v>0.9099999999999984</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7">
       <c r="A101">
-        <v>1071</v>
+        <v>573</v>
       </c>
       <c r="B101" t="s">
         <v>83</v>
@@ -3259,228 +3237,228 @@
         <v>30003662</v>
       </c>
       <c r="D101" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="E101">
-        <v>8.34</v>
+        <v>40.66792756223637</v>
       </c>
       <c r="F101" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="G101">
-        <v>8.34</v>
-      </c>
-    </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.2">
+        <v>40.66792756223637</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7">
       <c r="A102">
-        <v>1071</v>
+        <v>637</v>
       </c>
       <c r="B102" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C102">
         <v>30003662</v>
       </c>
       <c r="D102" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="E102">
-        <v>797.8437742326123</v>
+        <v>120</v>
       </c>
       <c r="F102" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="G102">
-        <v>176.0520724377636</v>
-      </c>
-    </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.2">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7">
       <c r="A103">
-        <v>924</v>
+        <v>637</v>
       </c>
       <c r="B103" t="s">
         <v>84</v>
       </c>
       <c r="C103">
-        <v>30005710</v>
+        <v>30003662</v>
       </c>
       <c r="D103" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E103">
-        <v>54.786758271991808</v>
+        <v>260.62</v>
       </c>
       <c r="F103" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="G103">
-        <v>7.360000000000003</v>
-      </c>
-    </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.2">
+        <v>260.62</v>
+      </c>
+    </row>
+    <row r="104" spans="1:7">
       <c r="A104">
-        <v>1101</v>
+        <v>1071</v>
       </c>
       <c r="B104" t="s">
-        <v>59</v>
+        <v>85</v>
       </c>
       <c r="C104">
-        <v>30005710</v>
+        <v>30003662</v>
       </c>
       <c r="D104" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E104">
-        <v>10.4</v>
+        <v>8.34</v>
       </c>
       <c r="F104" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="G104">
-        <v>10.4</v>
-      </c>
-    </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.2">
+        <v>8.34</v>
+      </c>
+    </row>
+    <row r="105" spans="1:7">
       <c r="A105">
-        <v>557</v>
+        <v>1071</v>
       </c>
       <c r="B105" t="s">
         <v>85</v>
       </c>
       <c r="C105">
-        <v>30005712</v>
+        <v>30003662</v>
       </c>
       <c r="D105" t="s">
         <v>160</v>
       </c>
       <c r="E105">
-        <v>19.194198914824479</v>
+        <v>797.8437742326123</v>
       </c>
       <c r="F105" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="G105">
-        <v>19.194198914824479</v>
-      </c>
-    </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.2">
+        <v>179.5420724377636</v>
+      </c>
+    </row>
+    <row r="106" spans="1:7">
       <c r="A106">
-        <v>775</v>
+        <v>930</v>
       </c>
       <c r="B106" t="s">
         <v>86</v>
       </c>
       <c r="C106">
+        <v>30005710</v>
+      </c>
+      <c r="D106" t="s">
+        <v>161</v>
+      </c>
+      <c r="E106">
+        <v>9.565990099748548</v>
+      </c>
+      <c r="F106" t="s">
+        <v>181</v>
+      </c>
+      <c r="G106">
+        <v>7.360000000000003</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7">
+      <c r="A107">
+        <v>1101</v>
+      </c>
+      <c r="B107" t="s">
+        <v>62</v>
+      </c>
+      <c r="C107">
+        <v>30005710</v>
+      </c>
+      <c r="D107" t="s">
+        <v>161</v>
+      </c>
+      <c r="E107">
+        <v>10.4</v>
+      </c>
+      <c r="F107" t="s">
+        <v>182</v>
+      </c>
+      <c r="G107">
+        <v>10.4</v>
+      </c>
+    </row>
+    <row r="108" spans="1:7">
+      <c r="A108">
+        <v>557</v>
+      </c>
+      <c r="B108" t="s">
+        <v>87</v>
+      </c>
+      <c r="C108">
         <v>30005712</v>
       </c>
-      <c r="D106" t="s">
-        <v>160</v>
-      </c>
-      <c r="E106">
-        <v>24.90307194181446</v>
-      </c>
-      <c r="F106" t="s">
-        <v>179</v>
-      </c>
-      <c r="G106">
-        <v>24.90307194181446</v>
-      </c>
-    </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A107">
+      <c r="D108" t="s">
+        <v>162</v>
+      </c>
+      <c r="E108">
+        <v>19.19419891482448</v>
+      </c>
+      <c r="F108" t="s">
+        <v>181</v>
+      </c>
+      <c r="G108">
+        <v>19.19419891482448</v>
+      </c>
+    </row>
+    <row r="109" spans="1:7">
+      <c r="A109">
         <v>1182</v>
       </c>
-      <c r="B107" t="s">
-        <v>87</v>
-      </c>
-      <c r="C107">
+      <c r="B109" t="s">
+        <v>88</v>
+      </c>
+      <c r="C109">
         <v>30005712</v>
       </c>
-      <c r="D107" t="s">
-        <v>160</v>
-      </c>
-      <c r="E107">
-        <v>258.57624387116829</v>
-      </c>
-      <c r="F107" t="s">
-        <v>179</v>
-      </c>
-      <c r="G107">
-        <v>9.2427291433610641</v>
-      </c>
-    </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A108">
+      <c r="D109" t="s">
+        <v>162</v>
+      </c>
+      <c r="E109">
+        <v>258.5762438711683</v>
+      </c>
+      <c r="F109" t="s">
+        <v>181</v>
+      </c>
+      <c r="G109">
+        <v>34.14580108517552</v>
+      </c>
+    </row>
+    <row r="110" spans="1:7">
+      <c r="A110">
         <v>223</v>
       </c>
-      <c r="B108" t="s">
-        <v>88</v>
-      </c>
-      <c r="C108">
-        <v>30003665</v>
-      </c>
-      <c r="D108" t="s">
-        <v>161</v>
-      </c>
-      <c r="E108">
-        <v>20</v>
-      </c>
-      <c r="F108" t="s">
-        <v>181</v>
-      </c>
-      <c r="G108">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A109">
-        <v>345</v>
-      </c>
-      <c r="B109" t="s">
+      <c r="B110" t="s">
         <v>89</v>
-      </c>
-      <c r="C109">
-        <v>30003665</v>
-      </c>
-      <c r="D109" t="s">
-        <v>161</v>
-      </c>
-      <c r="E109">
-        <v>46</v>
-      </c>
-      <c r="F109" t="s">
-        <v>180</v>
-      </c>
-      <c r="G109">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A110">
-        <v>389</v>
-      </c>
-      <c r="B110" t="s">
-        <v>50</v>
       </c>
       <c r="C110">
         <v>30003665</v>
       </c>
       <c r="D110" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="E110">
-        <v>209.56</v>
+        <v>20</v>
       </c>
       <c r="F110" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="G110">
-        <v>4.6599999999999966</v>
-      </c>
-    </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="111" spans="1:7">
       <c r="A111">
-        <v>398</v>
+        <v>345</v>
       </c>
       <c r="B111" t="s">
         <v>90</v>
@@ -3489,44 +3467,44 @@
         <v>30003665</v>
       </c>
       <c r="D111" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="E111">
-        <v>86</v>
+        <v>46</v>
       </c>
       <c r="F111" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="G111">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.2">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="112" spans="1:7">
       <c r="A112">
-        <v>430</v>
+        <v>389</v>
       </c>
       <c r="B112" t="s">
-        <v>91</v>
+        <v>53</v>
       </c>
       <c r="C112">
         <v>30003665</v>
       </c>
       <c r="D112" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="E112">
-        <v>20</v>
+        <v>209.56</v>
       </c>
       <c r="F112" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="G112">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.2">
+        <v>4.659999999999997</v>
+      </c>
+    </row>
+    <row r="113" spans="1:7">
       <c r="A113">
-        <v>430</v>
+        <v>398</v>
       </c>
       <c r="B113" t="s">
         <v>91</v>
@@ -3535,203 +3513,203 @@
         <v>30003665</v>
       </c>
       <c r="D113" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="E113">
+        <v>86</v>
+      </c>
+      <c r="F113" t="s">
+        <v>182</v>
+      </c>
+      <c r="G113">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="114" spans="1:7">
+      <c r="A114">
+        <v>430</v>
+      </c>
+      <c r="B114" t="s">
+        <v>92</v>
+      </c>
+      <c r="C114">
+        <v>30003665</v>
+      </c>
+      <c r="D114" t="s">
+        <v>163</v>
+      </c>
+      <c r="E114">
         <v>20</v>
       </c>
-      <c r="F113" t="s">
-        <v>181</v>
-      </c>
-      <c r="G113">
+      <c r="F114" t="s">
+        <v>182</v>
+      </c>
+      <c r="G114">
         <v>20</v>
       </c>
     </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A114">
-        <v>825</v>
-      </c>
-      <c r="B114" t="s">
-        <v>49</v>
-      </c>
-      <c r="C114">
-        <v>30003666</v>
-      </c>
-      <c r="D114" t="s">
-        <v>162</v>
-      </c>
-      <c r="E114">
-        <v>128</v>
-      </c>
-      <c r="F114" t="s">
-        <v>180</v>
-      </c>
-      <c r="G114">
-        <v>116.6</v>
-      </c>
-    </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:7">
       <c r="A115">
-        <v>524</v>
+        <v>430</v>
       </c>
       <c r="B115" t="s">
-        <v>41</v>
+        <v>92</v>
       </c>
       <c r="C115">
-        <v>30005711</v>
+        <v>30003665</v>
       </c>
       <c r="D115" t="s">
         <v>163</v>
       </c>
       <c r="E115">
-        <v>49.82</v>
+        <v>20</v>
       </c>
       <c r="F115" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="G115">
-        <v>34.299999999999997</v>
-      </c>
-    </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="116" spans="1:7">
       <c r="A116">
-        <v>472</v>
+        <v>825</v>
       </c>
       <c r="B116" t="s">
-        <v>92</v>
+        <v>52</v>
       </c>
       <c r="C116">
-        <v>30003669</v>
+        <v>30003666</v>
       </c>
       <c r="D116" t="s">
         <v>164</v>
       </c>
       <c r="E116">
-        <v>90.81</v>
+        <v>128</v>
       </c>
       <c r="F116" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="G116">
-        <v>90.81</v>
-      </c>
-    </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.2">
+        <v>116.6</v>
+      </c>
+    </row>
+    <row r="117" spans="1:7">
       <c r="A117">
+        <v>524</v>
+      </c>
+      <c r="B117" t="s">
+        <v>44</v>
+      </c>
+      <c r="C117">
+        <v>30005711</v>
+      </c>
+      <c r="D117" t="s">
+        <v>165</v>
+      </c>
+      <c r="E117">
+        <v>49.82</v>
+      </c>
+      <c r="F117" t="s">
+        <v>183</v>
+      </c>
+      <c r="G117">
+        <v>34.3</v>
+      </c>
+    </row>
+    <row r="118" spans="1:7">
+      <c r="A118">
         <v>472</v>
-      </c>
-      <c r="B117" t="s">
-        <v>92</v>
-      </c>
-      <c r="C117">
-        <v>30003669</v>
-      </c>
-      <c r="D117" t="s">
-        <v>164</v>
-      </c>
-      <c r="E117">
-        <v>71.400000000000006</v>
-      </c>
-      <c r="F117" t="s">
-        <v>181</v>
-      </c>
-      <c r="G117">
-        <v>2.8100000000000018</v>
-      </c>
-    </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A118">
-        <v>805</v>
       </c>
       <c r="B118" t="s">
         <v>93</v>
       </c>
       <c r="C118">
+        <v>30003669</v>
+      </c>
+      <c r="D118" t="s">
+        <v>166</v>
+      </c>
+      <c r="E118">
+        <v>90.81</v>
+      </c>
+      <c r="F118" t="s">
+        <v>182</v>
+      </c>
+      <c r="G118">
+        <v>90.81</v>
+      </c>
+    </row>
+    <row r="119" spans="1:7">
+      <c r="A119">
+        <v>472</v>
+      </c>
+      <c r="B119" t="s">
+        <v>93</v>
+      </c>
+      <c r="C119">
+        <v>30003669</v>
+      </c>
+      <c r="D119" t="s">
+        <v>166</v>
+      </c>
+      <c r="E119">
+        <v>71.40000000000001</v>
+      </c>
+      <c r="F119" t="s">
+        <v>183</v>
+      </c>
+      <c r="G119">
+        <v>2.810000000000002</v>
+      </c>
+    </row>
+    <row r="120" spans="1:7">
+      <c r="A120">
+        <v>805</v>
+      </c>
+      <c r="B120" t="s">
+        <v>94</v>
+      </c>
+      <c r="C120">
         <v>30005718</v>
       </c>
-      <c r="D118" t="s">
-        <v>165</v>
-      </c>
-      <c r="E118">
-        <v>8.3010239806048194</v>
-      </c>
-      <c r="F118" t="s">
-        <v>179</v>
-      </c>
-      <c r="G118">
-        <v>8.3010239806048194</v>
-      </c>
-    </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A119">
-        <v>1185</v>
-      </c>
-      <c r="B119" t="s">
-        <v>94</v>
-      </c>
-      <c r="C119">
-        <v>30005718</v>
-      </c>
-      <c r="D119" t="s">
-        <v>165</v>
-      </c>
-      <c r="E119">
-        <v>8.3010239806048194</v>
-      </c>
-      <c r="F119" t="s">
-        <v>179</v>
-      </c>
-      <c r="G119">
-        <v>8.3010239806048194</v>
-      </c>
-    </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A120">
+      <c r="D120" t="s">
+        <v>167</v>
+      </c>
+      <c r="E120">
+        <v>8.301023980604819</v>
+      </c>
+      <c r="F120" t="s">
+        <v>181</v>
+      </c>
+      <c r="G120">
+        <v>8.301023980604819</v>
+      </c>
+    </row>
+    <row r="121" spans="1:7">
+      <c r="A121">
         <v>202</v>
       </c>
-      <c r="B120" t="s">
+      <c r="B121" t="s">
         <v>95</v>
-      </c>
-      <c r="C120">
-        <v>30003671</v>
-      </c>
-      <c r="D120" t="s">
-        <v>166</v>
-      </c>
-      <c r="E120">
-        <v>199.37200000000001</v>
-      </c>
-      <c r="F120" t="s">
-        <v>181</v>
-      </c>
-      <c r="G120">
-        <v>199.37200000000001</v>
-      </c>
-    </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A121">
-        <v>281</v>
-      </c>
-      <c r="B121" t="s">
-        <v>69</v>
       </c>
       <c r="C121">
         <v>30003671</v>
       </c>
       <c r="D121" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="E121">
-        <v>1349.5440702733431</v>
+        <v>199.372</v>
       </c>
       <c r="F121" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="G121">
-        <v>58.47691573249341</v>
-      </c>
-    </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.2">
+        <v>199.372</v>
+      </c>
+    </row>
+    <row r="122" spans="1:7">
       <c r="A122">
         <v>613</v>
       </c>
@@ -3742,19 +3720,19 @@
         <v>30003671</v>
       </c>
       <c r="D122" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="E122">
         <v>4.92</v>
       </c>
       <c r="F122" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="G122">
         <v>4.92</v>
       </c>
     </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:7">
       <c r="A123">
         <v>649</v>
       </c>
@@ -3765,19 +3743,19 @@
         <v>30003671</v>
       </c>
       <c r="D123" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="E123">
-        <v>6.1300000000000026</v>
+        <v>6.130000000000003</v>
       </c>
       <c r="F123" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="G123">
-        <v>6.1300000000000026</v>
-      </c>
-    </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.2">
+        <v>6.130000000000003</v>
+      </c>
+    </row>
+    <row r="124" spans="1:7">
       <c r="A124">
         <v>649</v>
       </c>
@@ -3788,19 +3766,19 @@
         <v>30003671</v>
       </c>
       <c r="D124" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="E124">
-        <v>1.3549999999999991</v>
+        <v>1.354999999999999</v>
       </c>
       <c r="F124" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="G124">
-        <v>1.3549999999999991</v>
-      </c>
-    </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.2">
+        <v>1.354999999999999</v>
+      </c>
+    </row>
+    <row r="125" spans="1:7">
       <c r="A125">
         <v>702</v>
       </c>
@@ -3811,21 +3789,21 @@
         <v>30003671</v>
       </c>
       <c r="D125" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="E125">
         <v>12.95608426750653</v>
       </c>
       <c r="F125" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="G125">
         <v>12.95608426750653</v>
       </c>
     </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:7">
       <c r="A126">
-        <v>811</v>
+        <v>719</v>
       </c>
       <c r="B126" t="s">
         <v>99</v>
@@ -3834,90 +3812,90 @@
         <v>30003671</v>
       </c>
       <c r="D126" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="E126">
-        <v>14.45</v>
+        <v>2.85851618564382</v>
       </c>
       <c r="F126" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="G126">
-        <v>14.45</v>
-      </c>
-    </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.2">
+        <v>2.85851618564382</v>
+      </c>
+    </row>
+    <row r="127" spans="1:7">
       <c r="A127">
         <v>811</v>
       </c>
       <c r="B127" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C127">
         <v>30003671</v>
       </c>
       <c r="D127" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="E127">
-        <v>17.05</v>
+        <v>14.45</v>
       </c>
       <c r="F127" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="G127">
-        <v>17.05</v>
-      </c>
-    </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.2">
+        <v>14.45</v>
+      </c>
+    </row>
+    <row r="128" spans="1:7">
       <c r="A128">
-        <v>544</v>
+        <v>811</v>
       </c>
       <c r="B128" t="s">
         <v>100</v>
       </c>
       <c r="C128">
-        <v>30005727</v>
+        <v>30003671</v>
       </c>
       <c r="D128" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E128">
-        <v>66.34</v>
+        <v>17.05</v>
       </c>
       <c r="F128" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="G128">
-        <v>66.34</v>
-      </c>
-    </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.2">
+        <v>17.05</v>
+      </c>
+    </row>
+    <row r="129" spans="1:7">
       <c r="A129">
-        <v>544</v>
+        <v>811</v>
       </c>
       <c r="B129" t="s">
         <v>100</v>
       </c>
       <c r="C129">
-        <v>30005727</v>
+        <v>30003671</v>
       </c>
       <c r="D129" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E129">
-        <v>1529.463152511157</v>
+        <v>1550.33783613974</v>
       </c>
       <c r="F129" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="G129">
-        <v>24.149094149720341</v>
-      </c>
-    </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.2">
+        <v>55.61839954684964</v>
+      </c>
+    </row>
+    <row r="130" spans="1:7">
       <c r="A130">
-        <v>960</v>
+        <v>544</v>
       </c>
       <c r="B130" t="s">
         <v>101</v>
@@ -3926,572 +3904,663 @@
         <v>30005727</v>
       </c>
       <c r="D130" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="E130">
-        <v>1.090585027966124E-2</v>
+        <v>66.34</v>
       </c>
       <c r="F130" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="G130">
-        <v>1.090585027966124E-2</v>
-      </c>
-    </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.2">
+        <v>66.34</v>
+      </c>
+    </row>
+    <row r="131" spans="1:7">
       <c r="A131">
+        <v>544</v>
+      </c>
+      <c r="B131" t="s">
+        <v>101</v>
+      </c>
+      <c r="C131">
+        <v>30005727</v>
+      </c>
+      <c r="D131" t="s">
+        <v>169</v>
+      </c>
+      <c r="E131">
+        <v>1529.463152511157</v>
+      </c>
+      <c r="F131" t="s">
+        <v>181</v>
+      </c>
+      <c r="G131">
+        <v>24.14909414972034</v>
+      </c>
+    </row>
+    <row r="132" spans="1:7">
+      <c r="A132">
+        <v>960</v>
+      </c>
+      <c r="B132" t="s">
+        <v>102</v>
+      </c>
+      <c r="C132">
+        <v>30005727</v>
+      </c>
+      <c r="D132" t="s">
+        <v>169</v>
+      </c>
+      <c r="E132">
+        <v>0.01090585027966124</v>
+      </c>
+      <c r="F132" t="s">
+        <v>181</v>
+      </c>
+      <c r="G132">
+        <v>0.01090585027966124</v>
+      </c>
+    </row>
+    <row r="133" spans="1:7">
+      <c r="A133">
+        <v>985</v>
+      </c>
+      <c r="B133" t="s">
+        <v>38</v>
+      </c>
+      <c r="C133">
+        <v>30005729</v>
+      </c>
+      <c r="D133" t="s">
+        <v>170</v>
+      </c>
+      <c r="E133">
+        <v>30.2290728385165</v>
+      </c>
+      <c r="F133" t="s">
+        <v>181</v>
+      </c>
+      <c r="G133">
+        <v>2.8790728385165</v>
+      </c>
+    </row>
+    <row r="134" spans="1:7">
+      <c r="A134">
         <v>402</v>
       </c>
-      <c r="B131" t="s">
-        <v>102</v>
-      </c>
-      <c r="C131">
+      <c r="B134" t="s">
+        <v>103</v>
+      </c>
+      <c r="C134">
         <v>30005730</v>
       </c>
-      <c r="D131" t="s">
-        <v>168</v>
-      </c>
-      <c r="E131">
-        <v>151.14536419258249</v>
-      </c>
-      <c r="F131" t="s">
-        <v>179</v>
-      </c>
-      <c r="G131">
-        <v>151.14536419258249</v>
-      </c>
-    </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A132">
+      <c r="D134" t="s">
+        <v>171</v>
+      </c>
+      <c r="E134">
+        <v>151.1453641925825</v>
+      </c>
+      <c r="F134" t="s">
+        <v>181</v>
+      </c>
+      <c r="G134">
+        <v>151.1453641925825</v>
+      </c>
+    </row>
+    <row r="135" spans="1:7">
+      <c r="A135">
         <v>975</v>
       </c>
-      <c r="B132" t="s">
-        <v>103</v>
-      </c>
-      <c r="C132">
+      <c r="B135" t="s">
+        <v>104</v>
+      </c>
+      <c r="C135">
         <v>30005730</v>
-      </c>
-      <c r="D132" t="s">
-        <v>168</v>
-      </c>
-      <c r="E132">
-        <v>118.8089473817824</v>
-      </c>
-      <c r="F132" t="s">
-        <v>179</v>
-      </c>
-      <c r="G132">
-        <v>118.8089473817824</v>
-      </c>
-    </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A133">
-        <v>1128</v>
-      </c>
-      <c r="B133" t="s">
-        <v>104</v>
-      </c>
-      <c r="C133">
-        <v>30005735</v>
-      </c>
-      <c r="D133" t="s">
-        <v>169</v>
-      </c>
-      <c r="E133">
-        <v>26.891328185209129</v>
-      </c>
-      <c r="F133" t="s">
-        <v>179</v>
-      </c>
-      <c r="G133">
-        <v>26.891328185209129</v>
-      </c>
-    </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A134">
-        <v>1164</v>
-      </c>
-      <c r="B134" t="s">
-        <v>105</v>
-      </c>
-      <c r="C134">
-        <v>30005736</v>
-      </c>
-      <c r="D134" t="s">
-        <v>170</v>
-      </c>
-      <c r="E134">
-        <v>8.7664311231697862</v>
-      </c>
-      <c r="F134" t="s">
-        <v>179</v>
-      </c>
-      <c r="G134">
-        <v>8.7664311231697862</v>
-      </c>
-    </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A135">
-        <v>88</v>
-      </c>
-      <c r="B135" t="s">
-        <v>63</v>
-      </c>
-      <c r="C135">
-        <v>30003694</v>
       </c>
       <c r="D135" t="s">
         <v>171</v>
       </c>
       <c r="E135">
-        <v>80</v>
+        <v>118.8089473817824</v>
       </c>
       <c r="F135" t="s">
         <v>181</v>
       </c>
       <c r="G135">
-        <v>31.259000000000128</v>
-      </c>
-    </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.2">
+        <v>118.8089473817824</v>
+      </c>
+    </row>
+    <row r="136" spans="1:7">
       <c r="A136">
-        <v>89</v>
+        <v>1128</v>
       </c>
       <c r="B136" t="s">
+        <v>105</v>
+      </c>
+      <c r="C136">
+        <v>30005735</v>
+      </c>
+      <c r="D136" t="s">
+        <v>172</v>
+      </c>
+      <c r="E136">
+        <v>26.89132818520913</v>
+      </c>
+      <c r="F136" t="s">
+        <v>181</v>
+      </c>
+      <c r="G136">
+        <v>26.89132818520913</v>
+      </c>
+    </row>
+    <row r="137" spans="1:7">
+      <c r="A137">
+        <v>1164</v>
+      </c>
+      <c r="B137" t="s">
         <v>106</v>
       </c>
-      <c r="C136">
-        <v>30003694</v>
-      </c>
-      <c r="D136" t="s">
-        <v>171</v>
-      </c>
-      <c r="E136">
-        <v>797.96</v>
-      </c>
-      <c r="F136" t="s">
-        <v>181</v>
-      </c>
-      <c r="G136">
-        <v>797.96</v>
-      </c>
-    </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A137">
-        <v>212</v>
-      </c>
-      <c r="B137" t="s">
-        <v>107</v>
-      </c>
       <c r="C137">
-        <v>30003694</v>
+        <v>30005736</v>
       </c>
       <c r="D137" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="E137">
-        <v>55.68</v>
+        <v>8.766431123169786</v>
       </c>
       <c r="F137" t="s">
         <v>181</v>
       </c>
       <c r="G137">
-        <v>55.68</v>
-      </c>
-    </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.2">
+        <v>8.766431123169786</v>
+      </c>
+    </row>
+    <row r="138" spans="1:7">
       <c r="A138">
-        <v>237</v>
+        <v>88</v>
       </c>
       <c r="B138" t="s">
-        <v>108</v>
+        <v>66</v>
       </c>
       <c r="C138">
         <v>30003694</v>
       </c>
       <c r="D138" t="s">
-        <v>171</v>
+        <v>113</v>
       </c>
       <c r="E138">
-        <v>2.6869999999999998</v>
+        <v>80</v>
       </c>
       <c r="F138" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="G138">
-        <v>2.6869999999999998</v>
-      </c>
-    </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.2">
+        <v>49.41831249266545</v>
+      </c>
+    </row>
+    <row r="139" spans="1:7">
       <c r="A139">
-        <v>257</v>
+        <v>89</v>
       </c>
       <c r="B139" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C139">
         <v>30003694</v>
       </c>
       <c r="D139" t="s">
-        <v>171</v>
+        <v>113</v>
       </c>
       <c r="E139">
-        <v>18.390222775105929</v>
+        <v>797.96</v>
       </c>
       <c r="F139" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="G139">
-        <v>18.390222775105929</v>
-      </c>
-    </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.2">
+        <v>797.96</v>
+      </c>
+    </row>
+    <row r="140" spans="1:7">
       <c r="A140">
-        <v>267</v>
+        <v>212</v>
       </c>
       <c r="B140" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C140">
         <v>30003694</v>
       </c>
       <c r="D140" t="s">
-        <v>171</v>
+        <v>113</v>
       </c>
       <c r="E140">
-        <v>12.5</v>
+        <v>55.68</v>
       </c>
       <c r="F140" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="G140">
-        <v>12.5</v>
-      </c>
-    </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.2">
+        <v>55.68</v>
+      </c>
+    </row>
+    <row r="141" spans="1:7">
       <c r="A141">
-        <v>281</v>
+        <v>237</v>
       </c>
       <c r="B141" t="s">
-        <v>69</v>
+        <v>109</v>
       </c>
       <c r="C141">
         <v>30003694</v>
       </c>
       <c r="D141" t="s">
-        <v>171</v>
+        <v>113</v>
       </c>
       <c r="E141">
-        <v>16.5</v>
+        <v>2.687</v>
       </c>
       <c r="F141" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="G141">
-        <v>16.5</v>
-      </c>
-    </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.2">
+        <v>2.687</v>
+      </c>
+    </row>
+    <row r="142" spans="1:7">
       <c r="A142">
-        <v>321</v>
+        <v>257</v>
       </c>
       <c r="B142" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C142">
         <v>30003694</v>
       </c>
       <c r="D142" t="s">
-        <v>171</v>
+        <v>113</v>
       </c>
       <c r="E142">
-        <v>8.6300000000000026</v>
+        <v>18.39022277510593</v>
       </c>
       <c r="F142" t="s">
         <v>181</v>
       </c>
       <c r="G142">
-        <v>8.6300000000000026</v>
-      </c>
-    </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.2">
+        <v>18.39022277510593</v>
+      </c>
+    </row>
+    <row r="143" spans="1:7">
       <c r="A143">
-        <v>369</v>
+        <v>267</v>
       </c>
       <c r="B143" t="s">
-        <v>39</v>
+        <v>111</v>
       </c>
       <c r="C143">
         <v>30003694</v>
       </c>
       <c r="D143" t="s">
-        <v>171</v>
+        <v>113</v>
       </c>
       <c r="E143">
-        <v>29.04</v>
+        <v>12.5</v>
       </c>
       <c r="F143" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="G143">
-        <v>21.34</v>
-      </c>
-    </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.2">
+        <v>12.5</v>
+      </c>
+    </row>
+    <row r="144" spans="1:7">
       <c r="A144">
-        <v>445</v>
+        <v>281</v>
       </c>
       <c r="B144" t="s">
-        <v>23</v>
+        <v>73</v>
       </c>
       <c r="C144">
         <v>30003694</v>
       </c>
       <c r="D144" t="s">
-        <v>171</v>
+        <v>113</v>
       </c>
       <c r="E144">
-        <v>145.61000000000001</v>
+        <v>16.5</v>
       </c>
       <c r="F144" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="G144">
-        <v>27.403777224893929</v>
-      </c>
-    </row>
-    <row r="145" spans="1:7" x14ac:dyDescent="0.2">
+        <v>16.5</v>
+      </c>
+    </row>
+    <row r="145" spans="1:7">
       <c r="A145">
-        <v>592</v>
+        <v>321</v>
       </c>
       <c r="B145" t="s">
         <v>112</v>
       </c>
       <c r="C145">
-        <v>30003695</v>
+        <v>30003694</v>
       </c>
       <c r="D145" t="s">
-        <v>172</v>
+        <v>113</v>
       </c>
       <c r="E145">
-        <v>200</v>
+        <v>8.630000000000003</v>
       </c>
       <c r="F145" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="G145">
-        <v>75.180000000000007</v>
-      </c>
-    </row>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.2">
+        <v>8.630000000000003</v>
+      </c>
+    </row>
+    <row r="146" spans="1:7">
       <c r="A146">
+        <v>369</v>
+      </c>
+      <c r="B146" t="s">
+        <v>42</v>
+      </c>
+      <c r="C146">
+        <v>30003694</v>
+      </c>
+      <c r="D146" t="s">
+        <v>113</v>
+      </c>
+      <c r="E146">
+        <v>29.04</v>
+      </c>
+      <c r="F146" t="s">
+        <v>183</v>
+      </c>
+      <c r="G146">
+        <v>21.34</v>
+      </c>
+    </row>
+    <row r="147" spans="1:7">
+      <c r="A147">
+        <v>445</v>
+      </c>
+      <c r="B147" t="s">
+        <v>23</v>
+      </c>
+      <c r="C147">
+        <v>30003694</v>
+      </c>
+      <c r="D147" t="s">
+        <v>113</v>
+      </c>
+      <c r="E147">
+        <v>145.61</v>
+      </c>
+      <c r="F147" t="s">
+        <v>183</v>
+      </c>
+      <c r="G147">
+        <v>5.469999999999999</v>
+      </c>
+    </row>
+    <row r="148" spans="1:7">
+      <c r="A148">
+        <v>787</v>
+      </c>
+      <c r="B148" t="s">
+        <v>113</v>
+      </c>
+      <c r="C148">
+        <v>30003694</v>
+      </c>
+      <c r="D148" t="s">
+        <v>113</v>
+      </c>
+      <c r="E148">
+        <v>3.774464732228565</v>
+      </c>
+      <c r="F148" t="s">
+        <v>181</v>
+      </c>
+      <c r="G148">
+        <v>3.774464732228565</v>
+      </c>
+    </row>
+    <row r="149" spans="1:7">
+      <c r="A149">
         <v>592</v>
-      </c>
-      <c r="B146" t="s">
-        <v>112</v>
-      </c>
-      <c r="C146">
-        <v>30003696</v>
-      </c>
-      <c r="D146" t="s">
-        <v>173</v>
-      </c>
-      <c r="E146">
-        <v>200</v>
-      </c>
-      <c r="F146" t="s">
-        <v>180</v>
-      </c>
-      <c r="G146">
-        <v>75.040000000000006</v>
-      </c>
-    </row>
-    <row r="147" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A147">
-        <v>377</v>
-      </c>
-      <c r="B147" t="s">
-        <v>113</v>
-      </c>
-      <c r="C147">
-        <v>30005745</v>
-      </c>
-      <c r="D147" t="s">
-        <v>174</v>
-      </c>
-      <c r="E147">
-        <v>36.766453060826628</v>
-      </c>
-      <c r="F147" t="s">
-        <v>179</v>
-      </c>
-      <c r="G147">
-        <v>36.766453060826628</v>
-      </c>
-    </row>
-    <row r="148" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A148">
-        <v>202</v>
-      </c>
-      <c r="B148" t="s">
-        <v>95</v>
-      </c>
-      <c r="C148">
-        <v>30003698</v>
-      </c>
-      <c r="D148" t="s">
-        <v>175</v>
-      </c>
-      <c r="E148">
-        <v>2093.352485221164</v>
-      </c>
-      <c r="F148" t="s">
-        <v>179</v>
-      </c>
-      <c r="G148">
-        <v>996.49636554605343</v>
-      </c>
-    </row>
-    <row r="149" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A149">
-        <v>203</v>
       </c>
       <c r="B149" t="s">
         <v>114</v>
       </c>
       <c r="C149">
-        <v>30003698</v>
+        <v>30003695</v>
       </c>
       <c r="D149" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E149">
-        <v>3.3009999999999948</v>
+        <v>200</v>
       </c>
       <c r="F149" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="G149">
-        <v>3.3009999999999948</v>
-      </c>
-    </row>
-    <row r="150" spans="1:7" x14ac:dyDescent="0.2">
+        <v>75.18000000000001</v>
+      </c>
+    </row>
+    <row r="150" spans="1:7">
       <c r="A150">
-        <v>332</v>
+        <v>592</v>
       </c>
       <c r="B150" t="s">
-        <v>71</v>
+        <v>114</v>
       </c>
       <c r="C150">
-        <v>30003698</v>
+        <v>30003696</v>
       </c>
       <c r="D150" t="s">
         <v>175</v>
       </c>
       <c r="E150">
-        <v>157.21</v>
+        <v>200</v>
       </c>
       <c r="F150" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="G150">
-        <v>157.21</v>
-      </c>
-    </row>
-    <row r="151" spans="1:7" x14ac:dyDescent="0.2">
+        <v>75.04000000000001</v>
+      </c>
+    </row>
+    <row r="151" spans="1:7">
       <c r="A151">
-        <v>538</v>
+        <v>377</v>
       </c>
       <c r="B151" t="s">
         <v>115</v>
       </c>
       <c r="C151">
+        <v>30005745</v>
+      </c>
+      <c r="D151" t="s">
+        <v>176</v>
+      </c>
+      <c r="E151">
+        <v>36.76645306082663</v>
+      </c>
+      <c r="F151" t="s">
+        <v>181</v>
+      </c>
+      <c r="G151">
+        <v>36.76645306082663</v>
+      </c>
+    </row>
+    <row r="152" spans="1:7">
+      <c r="A152">
+        <v>202</v>
+      </c>
+      <c r="B152" t="s">
+        <v>95</v>
+      </c>
+      <c r="C152">
         <v>30003698</v>
       </c>
-      <c r="D151" t="s">
-        <v>175</v>
-      </c>
-      <c r="E151">
-        <v>27.692634453946649</v>
-      </c>
-      <c r="F151" t="s">
-        <v>179</v>
-      </c>
-      <c r="G151">
-        <v>27.692634453946649</v>
-      </c>
-    </row>
-    <row r="152" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A152">
-        <v>461</v>
-      </c>
-      <c r="B152" t="s">
+      <c r="D152" t="s">
+        <v>177</v>
+      </c>
+      <c r="E152">
+        <v>2093.352485221164</v>
+      </c>
+      <c r="F152" t="s">
+        <v>181</v>
+      </c>
+      <c r="G152">
+        <v>996.4963655460534</v>
+      </c>
+    </row>
+    <row r="153" spans="1:7">
+      <c r="A153">
+        <v>203</v>
+      </c>
+      <c r="B153" t="s">
         <v>116</v>
       </c>
-      <c r="C152">
-        <v>30005755</v>
-      </c>
-      <c r="D152" t="s">
-        <v>176</v>
-      </c>
-      <c r="E152">
-        <v>22.671804628887379</v>
-      </c>
-      <c r="F152" t="s">
-        <v>179</v>
-      </c>
-      <c r="G152">
-        <v>22.671804628887379</v>
-      </c>
-    </row>
-    <row r="153" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A153">
-        <v>814</v>
-      </c>
-      <c r="B153" t="s">
-        <v>117</v>
-      </c>
       <c r="C153">
-        <v>30005757</v>
+        <v>30003698</v>
       </c>
       <c r="D153" t="s">
         <v>177</v>
       </c>
       <c r="E153">
-        <v>107.91331174786271</v>
+        <v>3.300999999999995</v>
       </c>
       <c r="F153" t="s">
+        <v>183</v>
+      </c>
+      <c r="G153">
+        <v>3.300999999999995</v>
+      </c>
+    </row>
+    <row r="154" spans="1:7">
+      <c r="A154">
+        <v>332</v>
+      </c>
+      <c r="B154" t="s">
+        <v>74</v>
+      </c>
+      <c r="C154">
+        <v>30003698</v>
+      </c>
+      <c r="D154" t="s">
+        <v>177</v>
+      </c>
+      <c r="E154">
+        <v>157.21</v>
+      </c>
+      <c r="F154" t="s">
+        <v>183</v>
+      </c>
+      <c r="G154">
+        <v>157.21</v>
+      </c>
+    </row>
+    <row r="155" spans="1:7">
+      <c r="A155">
+        <v>538</v>
+      </c>
+      <c r="B155" t="s">
+        <v>117</v>
+      </c>
+      <c r="C155">
+        <v>30003698</v>
+      </c>
+      <c r="D155" t="s">
+        <v>177</v>
+      </c>
+      <c r="E155">
+        <v>27.69263445394665</v>
+      </c>
+      <c r="F155" t="s">
+        <v>181</v>
+      </c>
+      <c r="G155">
+        <v>27.69263445394665</v>
+      </c>
+    </row>
+    <row r="156" spans="1:7">
+      <c r="A156">
+        <v>461</v>
+      </c>
+      <c r="B156" t="s">
+        <v>118</v>
+      </c>
+      <c r="C156">
+        <v>30005755</v>
+      </c>
+      <c r="D156" t="s">
+        <v>178</v>
+      </c>
+      <c r="E156">
+        <v>22.67180462888738</v>
+      </c>
+      <c r="F156" t="s">
+        <v>181</v>
+      </c>
+      <c r="G156">
+        <v>22.67180462888738</v>
+      </c>
+    </row>
+    <row r="157" spans="1:7">
+      <c r="A157">
+        <v>814</v>
+      </c>
+      <c r="B157" t="s">
+        <v>119</v>
+      </c>
+      <c r="C157">
+        <v>30005757</v>
+      </c>
+      <c r="D157" t="s">
         <v>179</v>
       </c>
-      <c r="G153">
+      <c r="E157">
+        <v>107.9133117478627</v>
+      </c>
+      <c r="F157" t="s">
+        <v>181</v>
+      </c>
+      <c r="G157">
         <v>42.66</v>
       </c>
     </row>
-    <row r="154" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A154">
+    <row r="158" spans="1:7">
+      <c r="A158">
         <v>945</v>
       </c>
-      <c r="B154" t="s">
-        <v>118</v>
-      </c>
-      <c r="C154">
+      <c r="B158" t="s">
+        <v>120</v>
+      </c>
+      <c r="C158">
         <v>30004223</v>
       </c>
-      <c r="D154" t="s">
-        <v>178</v>
-      </c>
-      <c r="E154">
-        <v>0.24353255793601691</v>
-      </c>
-      <c r="F154" t="s">
-        <v>179</v>
-      </c>
-      <c r="G154">
-        <v>0.24353255793601691</v>
+      <c r="D158" t="s">
+        <v>180</v>
+      </c>
+      <c r="E158">
+        <v>0.2435325579360169</v>
+      </c>
+      <c r="F158" t="s">
+        <v>181</v>
+      </c>
+      <c r="G158">
+        <v>0.2435325579360169</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G154" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>